--- a/underwriting/sample/Riverbend Apartments - Rent Roll.xlsx
+++ b/underwriting/sample/Riverbend Apartments - Rent Roll.xlsx
@@ -469,7 +469,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cedar Ridge Capital (demo) - fictional sample data</t>
+          <t>Portfolio Management Dashboard (demo) - fictional sample data</t>
         </is>
       </c>
     </row>
